--- a/artfynd/A 33142-2026 artfynd.xlsx
+++ b/artfynd/A 33142-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136023947</v>
       </c>
       <c r="B2" t="n">
-        <v>96501</v>
+        <v>96518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33142-2026 artfynd.xlsx
+++ b/artfynd/A 33142-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136023947</v>
       </c>
       <c r="B2" t="n">
-        <v>96518</v>
+        <v>96519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33142-2026 artfynd.xlsx
+++ b/artfynd/A 33142-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136023947</v>
       </c>
       <c r="B2" t="n">
-        <v>96519</v>
+        <v>96520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33142-2026 artfynd.xlsx
+++ b/artfynd/A 33142-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136023947</v>
       </c>
       <c r="B2" t="n">
-        <v>96520</v>
+        <v>96521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33142-2026 artfynd.xlsx
+++ b/artfynd/A 33142-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136023947</v>
       </c>
       <c r="B2" t="n">
-        <v>96521</v>
+        <v>96527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33142-2026 artfynd.xlsx
+++ b/artfynd/A 33142-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136023947</v>
       </c>
       <c r="B2" t="n">
-        <v>96527</v>
+        <v>96528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
